--- a/e2e/expectedData/sub_Master_Prorate_Others.xlsx
+++ b/e2e/expectedData/sub_Master_Prorate_Others.xlsx
@@ -59,7 +59,7 @@
     <t>RIMBUN SIBURIAN</t>
   </si>
   <si>
-    <t>Expat</t>
+    <t>Local</t>
   </si>
   <si>
     <t>IV</t>
@@ -80,7 +80,7 @@
     <t>Remark taxi online claim updated</t>
   </si>
   <si>
-    <t>DILI, 26 AGUSTUS 2026</t>
+    <t>DILI, 09 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>

--- a/e2e/expectedData/sub_Master_Prorate_Others.xlsx
+++ b/e2e/expectedData/sub_Master_Prorate_Others.xlsx
@@ -80,7 +80,7 @@
     <t>Remark taxi online claim updated</t>
   </si>
   <si>
-    <t>DILI, 09 SEPTEMBER 2026</t>
+    <t>DILI, 10 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
